--- a/config/title_type.xlsx
+++ b/config/title_type.xlsx
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>冒険</t>
+          <t>冒险</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
